--- a/cypress/downloads/relatorio_emprestimos.xlsx
+++ b/cypress/downloads/relatorio_emprestimos.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -836,12 +836,512 @@
         <v>10/10/2026 19:28</v>
       </c>
       <c r="F22" t="str">
+        <v>10/10/2026 19:29</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B23" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C23" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E23" t="str">
+        <v>10/10/2026 19:45</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10/10/2026 19:45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B24" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C24" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E24" t="str">
+        <v>10/10/2026 19:50</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10/10/2026 19:51</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B25" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C25" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E25" t="str">
+        <v>10/10/2026 19:52</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10/10/2026 19:53</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B26" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C26" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E26" t="str">
+        <v>10/10/2026 19:54</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10/10/2026 19:54</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B27" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C27" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E27" t="str">
+        <v>10/10/2026 19:56</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10/10/2026 20:00</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B28" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C28" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E28" t="str">
+        <v>10/10/2026 20:02</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10/10/2026 20:03</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B29" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C29" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E29" t="str">
+        <v>10/10/2026 20:05</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10/10/2026 20:05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B30" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C30" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E30" t="str">
+        <v>10/10/2026 20:07</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10/10/2026 20:08</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B31" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C31" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E31" t="str">
+        <v>18/10/2026 13:45</v>
+      </c>
+      <c r="F31" t="str">
+        <v>18/10/2026 13:47</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B32" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C32" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E32" t="str">
+        <v>18/10/2026 16:15</v>
+      </c>
+      <c r="F32" t="str">
+        <v>18/10/2026 16:15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B33" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C33" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E33" t="str">
+        <v>18/10/2026 16:16</v>
+      </c>
+      <c r="F33" t="str">
+        <v>18/10/2026 16:18</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B34" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C34" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E34" t="str">
+        <v>18/10/2026 16:21</v>
+      </c>
+      <c r="F34" t="str">
+        <v>18/10/2026 16:21</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B35" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C35" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E35" t="str">
+        <v>18/10/2026 16:22</v>
+      </c>
+      <c r="F35" t="str">
+        <v>18/10/2026 16:27</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B36" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C36" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E36" t="str">
+        <v>18/10/2026 16:27</v>
+      </c>
+      <c r="F36" t="str">
+        <v>18/10/2026 16:27</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B37" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C37" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E37" t="str">
+        <v>18/10/2026 16:29</v>
+      </c>
+      <c r="F37" t="str">
+        <v>18/10/2026 16:30</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B38" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C38" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E38" t="str">
+        <v>18/10/2026 16:31</v>
+      </c>
+      <c r="F38" t="str">
+        <v>18/10/2026 16:31</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B39" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C39" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E39" t="str">
+        <v>18/10/2026 16:32</v>
+      </c>
+      <c r="F39" t="str">
+        <v>18/10/2026 16:33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B40" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C40" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E40" t="str">
+        <v>18/10/2026 16:34</v>
+      </c>
+      <c r="F40" t="str">
+        <v>18/10/2026 16:34</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B41" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C41" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E41" t="str">
+        <v>18/10/2026 16:35</v>
+      </c>
+      <c r="F41" t="str">
+        <v>18/10/2026 16:37</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B42" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C42" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E42" t="str">
+        <v>18/10/2026 16:37</v>
+      </c>
+      <c r="F42" t="str">
+        <v>18/10/2026 16:37</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B43" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C43" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E43" t="str">
+        <v>18/10/2026 16:45</v>
+      </c>
+      <c r="F43" t="str">
+        <v>18/10/2026 16:45</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B44" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C44" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E44" t="str">
+        <v>18/10/2026 16:46</v>
+      </c>
+      <c r="F44" t="str">
+        <v>18/10/2026 16:50</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B45" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C45" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E45" t="str">
+        <v>18/10/2026 16:51</v>
+      </c>
+      <c r="F45" t="str">
+        <v>18/10/2026 16:52</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B46" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C46" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E46" t="str">
+        <v>18/10/2026 16:57</v>
+      </c>
+      <c r="F46" t="str">
+        <v>18/10/2026 16:57</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="B47" t="str">
+        <v>505233</v>
+      </c>
+      <c r="C47" t="str">
+        <v>TesteE2E</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Engenharia de Software</v>
+      </c>
+      <c r="E47" t="str">
+        <v>18/10/2026 16:59</v>
+      </c>
+      <c r="F47" t="str">
         <v>31/12/1969 21:00</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F47"/>
   </ignoredErrors>
 </worksheet>
 </file>